--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2881"/>
+  <dimension ref="A1:H2883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75350,7 +75350,59 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2882">
+      <c r="A2882" t="n">
+        <v>26063</v>
+      </c>
+      <c r="B2882" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2882" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2882" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2882" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2882" t="n">
+        <v>31</v>
+      </c>
+      <c r="G2882" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2882" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="n">
+        <v>26064</v>
+      </c>
+      <c r="B2883" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2883" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2883" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2883" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2883" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2883" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2883" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2885"/>
+  <dimension ref="A1:H2887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75454,6 +75454,58 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2886">
+      <c r="A2886" t="n">
+        <v>26067</v>
+      </c>
+      <c r="B2886" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2886" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2886" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2886" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2886" t="n">
+        <v>28</v>
+      </c>
+      <c r="G2886" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2886" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="n">
+        <v>26068</v>
+      </c>
+      <c r="B2887" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2887" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2887" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2887" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2887" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2887" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2887" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2887"/>
+  <dimension ref="A1:H2888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75506,6 +75506,32 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2888">
+      <c r="A2888" t="n">
+        <v>26069</v>
+      </c>
+      <c r="B2888" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2888" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2888" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2888" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2888" t="n">
+        <v>29</v>
+      </c>
+      <c r="G2888" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2888" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>

--- a/assets/data/DLT历史数据_适配模型版.xlsx
+++ b/assets/data/DLT历史数据_适配模型版.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2889"/>
+  <dimension ref="A1:H2890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75558,6 +75558,32 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2890">
+      <c r="A2890" t="n">
+        <v>26071</v>
+      </c>
+      <c r="B2890" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2890" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2890" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2890" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2890" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2890" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2890" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
